--- a/GruzoMaster/bin/Debug/Отчет.xlsx
+++ b/GruzoMaster/bin/Debug/Отчет.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>№</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Машина</t>
   </si>
   <si>
-    <t>Вес (кг)</t>
+    <t>Вес (т.)</t>
   </si>
   <si>
     <t>Обьем (см.3)</t>
@@ -37,10 +37,10 @@
     <t>Стоимость (Byn)</t>
   </si>
   <si>
-    <t>asdasdas</t>
-  </si>
-  <si>
-    <t>21.02.2025</t>
+    <t>Мебель</t>
+  </si>
+  <si>
+    <t>02.06.2025</t>
   </si>
   <si>
     <t>[о125мр719] Iveco Daily</t>
@@ -52,19 +52,10 @@
     <t>[х137ре799] Scania G440</t>
   </si>
   <si>
-    <t>[р517нк719] Sitrak C7H</t>
-  </si>
-  <si>
-    <t>[м131рн67] Mercedes Actros</t>
-  </si>
-  <si>
-    <t>[asd] Mercedes asdasd</t>
-  </si>
-  <si>
     <t>ИТОГО</t>
   </si>
   <si>
-    <t>Общий вес (кг)</t>
+    <t>Общий вес (т.)</t>
   </si>
   <si>
     <t>Общий обьем (см.3)</t>
@@ -73,10 +64,13 @@
     <t>Месяц</t>
   </si>
   <si>
-    <t>Объем (м³)</t>
-  </si>
-  <si>
-    <t>2025-02</t>
+    <t>Вес (т)</t>
+  </si>
+  <si>
+    <t>Объем (см³)</t>
+  </si>
+  <si>
+    <t>2025-06</t>
   </si>
 </sst>
 </file>
@@ -181,12 +175,12 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Отчет по грузам'!$C$2:$C$7</c:f>
+              <c:f>'Отчет по грузам'!$C$2:$C$4</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Отчет по грузам'!$E$2:$E$7</c:f>
+              <c:f>'Отчет по грузам'!$E$2:$E$4</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -274,7 +268,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr/>
-                  <a:t>Вес (кг)</a:t>
+                  <a:t>Вес (т.)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -383,12 +377,12 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'График по машинам'!$A$2:$A$7</c:f>
+              <c:f>'График по машинам'!$A$2:$A$4</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График по машинам'!$B$2:$B$7</c:f>
+              <c:f>'График по машинам'!$B$2:$B$4</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -474,7 +468,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr/>
-                  <a:t>Вес (кг)</a:t>
+                  <a:t>Вес (т)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -677,7 +671,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr/>
-                  <a:t>Вес (кг) и Объем (м³)</a:t>
+                  <a:t>Вес (т) и Объем (см³)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -839,13 +833,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="14.1701365879604" customWidth="1"/>
-    <col min="4" max="4" width="26.5430886404855" customWidth="1"/>
+    <col min="4" max="4" width="22.9449680873326" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="12.9455272129604" customWidth="1"/>
     <col min="7" max="7" width="15.7763486589704" customWidth="1"/>
@@ -888,13 +882,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G2" s="0">
-        <v>205</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3">
@@ -911,13 +905,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3" s="0">
-        <v>205</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="4">
@@ -934,97 +928,28 @@
         <v>11</v>
       </c>
       <c r="E4" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F4" s="0">
         <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>205</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F5" s="0">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5" s="0">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="0">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0">
-        <v>0</v>
-      </c>
-      <c r="G6" s="0">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="0">
-        <v>7</v>
-      </c>
-      <c r="F7" s="0">
-        <v>0</v>
-      </c>
-      <c r="G7" s="0">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="0">
-        <v>12</v>
-      </c>
-      <c r="F8" s="0">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0">
-        <v>1230</v>
+        <v>15000</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,10 +968,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -1054,10 +979,10 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1065,10 +990,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1076,42 +1001,9 @@
         <v>11</v>
       </c>
       <c r="B4" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="0">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="0">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="0">
-        <v>7</v>
-      </c>
-      <c r="C7" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1128,24 +1020,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="0">
+        <v>30</v>
+      </c>
+      <c r="C2" s="0">
         <v>20</v>
-      </c>
-      <c r="B2" s="0">
-        <v>12</v>
-      </c>
-      <c r="C2" s="0">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
